--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260812.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>115,043,947</t>
+          <t>7,469,103</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>7,469,103</t>
+          <t>115,043,947</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>15,768,393</t>
+          <t>276,275,180</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>276,275,180</t>
+          <t>15,768,393</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>26,645,240</t>
+          <t>72,212,646</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>72,212,646</t>
+          <t>26,645,240</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
